--- a/architectures and decision enablers/architecture decision enabler/cloud-security-posturing/Cloud_Security_Assessment.xlsx
+++ b/architectures and decision enablers/architecture decision enabler/cloud-security-posturing/Cloud_Security_Assessment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\architecture decision enabler\cloud-security-posturing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3BC0A8-5D80-4388-A306-B9CE2C895C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1663712B-AB23-48AC-9AFB-AA0E39E14C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D62D5DFD-F87A-4D1C-B4C2-9718B4BFE1A3}"/>
   </bookViews>
@@ -2097,73 +2097,6 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="8"/>
-        </left>
-        <right style="thin">
-          <color theme="8"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color theme="8"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="8"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2211,6 +2144,73 @@
         <bottom style="medium">
           <color rgb="FFDCDFE5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="8"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="8"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="8"/>
+        </left>
+        <right style="thin">
+          <color theme="8"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -2240,7 +2240,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Cloud_security_posturing.xlsx]Results!PivotTable1</c:name>
+    <c:name>[Cloud_Security_Assessment.xlsx]Results!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3732,13 +3732,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D90B28C5-67E5-426D-8A4B-D0120A7E64AD}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D90B28C5-67E5-426D-8A4B-D0120A7E64AD}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
   <autoFilter ref="A1:D76" xr:uid="{D90B28C5-67E5-426D-8A4B-D0120A7E64AD}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8431A441-4ECE-4A90-A222-02A773BE052E}" name="Category" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{95B0C528-7571-4ECB-9F08-6EFA807C316D}" name="Client-Specific Question" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{28F77A17-2EC1-4471-B442-2EE24E12C641}" name="User Priority" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{F1E6196C-5F62-481B-B30A-58A8AEDCBC71}" name="User Score" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{8431A441-4ECE-4A90-A222-02A773BE052E}" name="Category" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{95B0C528-7571-4ECB-9F08-6EFA807C316D}" name="Client-Specific Question" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{28F77A17-2EC1-4471-B442-2EE24E12C641}" name="User Priority" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{F1E6196C-5F62-481B-B30A-58A8AEDCBC71}" name="User Score" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(C2,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3760,12 +3760,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5F2DA1A1-3406-4AF6-98DD-0ED725F042BA}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5F2DA1A1-3406-4AF6-98DD-0ED725F042BA}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A1:C5" xr:uid="{5F2DA1A1-3406-4AF6-98DD-0ED725F042BA}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{F014942C-3959-42B4-BE32-78D0A70F5CF7}" name="States"/>
-    <tableColumn id="2" xr3:uid="{79FFC482-DD0D-4E1E-85E6-B2A80E0413F4}" name="Definitions" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{E69330B5-6666-488B-9EDC-D0D797F513EB}" name="Operational Impact" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{79FFC482-DD0D-4E1E-85E6-B2A80E0413F4}" name="Definitions" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{E69330B5-6666-488B-9EDC-D0D797F513EB}" name="Operational Impact" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
